--- a/education_surveys/028_flashcard_creation_survey--education_surveys.xlsx
+++ b/education_surveys/028_flashcard_creation_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Platforms Used</t>
+          <t>Platforms 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Platforms Used</t>
+          <t>Platforms 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Platforms Used</t>
+          <t>Platforms 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Platforms Used</t>
+          <t>Platforms 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1777,29 +1777,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>content_type_2_choices</t>
+          <t>platforms_other_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1811,148 +1811,250 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>platforms_1_choices</t>
+          <t>content_type_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>platforms_1_choices</t>
+          <t>content_type_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>platforms_2_choices</t>
+          <t>platforms_1_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>platforms_2_choices</t>
+          <t>platforms_1_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>platforms_3_choices</t>
+          <t>platforms_1_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>platforms_3_choices</t>
+          <t>platforms_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>platforms_4_choices</t>
+          <t>platforms_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>platforms_2_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>platforms_3_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>platforms_3_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>platforms_3_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>platforms_4_choices</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>platforms_4_choices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>platforms_4_choices</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
